--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1082"/>
+  <dimension ref="A1:C1085"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-12 06:48 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-13 07:06 UTC</t>
         </is>
       </c>
     </row>
@@ -16664,6 +16664,51 @@
       <c r="C1082" t="inlineStr">
         <is>
           <t>2026-09-12 06:48 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1083" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>2026-09-13 07:06 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1084" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>2026-09-13 07:06 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1085" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>2026-09-13 07:06 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1085"/>
+  <dimension ref="A1:C1088"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-13 07:06 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-14 07:29 UTC</t>
         </is>
       </c>
     </row>
@@ -16709,6 +16709,51 @@
       <c r="C1085" t="inlineStr">
         <is>
           <t>2026-09-13 07:06 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1086" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:29 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1087" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:29 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1088" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>2026-09-14 07:29 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1088"/>
+  <dimension ref="A1:C1091"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-14 07:29 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-15 07:07 UTC</t>
         </is>
       </c>
     </row>
@@ -16754,6 +16754,51 @@
       <c r="C1088" t="inlineStr">
         <is>
           <t>2026-09-14 07:29 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1089" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>2026-09-15 07:07 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1090" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>2026-09-15 07:07 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1091" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>2026-09-15 07:07 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1091"/>
+  <dimension ref="A1:C1094"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-15 07:07 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-16 07:07 UTC</t>
         </is>
       </c>
     </row>
@@ -16799,6 +16799,51 @@
       <c r="C1091" t="inlineStr">
         <is>
           <t>2026-09-15 07:07 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1092" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>2026-09-16 07:07 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1093" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>2026-09-16 07:07 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1094" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>2026-09-16 07:07 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1094"/>
+  <dimension ref="A1:C1097"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-16 07:07 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-17 07:06 UTC</t>
         </is>
       </c>
     </row>
@@ -16844,6 +16844,51 @@
       <c r="C1094" t="inlineStr">
         <is>
           <t>2026-09-16 07:07 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1095" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>2026-09-17 07:06 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1096" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>2026-09-17 07:06 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1097" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>2026-09-17 07:06 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1097"/>
+  <dimension ref="A1:C1100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-17 07:06 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-18 06:59 UTC</t>
         </is>
       </c>
     </row>
@@ -16889,6 +16889,51 @@
       <c r="C1097" t="inlineStr">
         <is>
           <t>2026-09-17 07:06 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1098" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>2026-09-18 06:59 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1099" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>2026-09-18 06:59 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1100" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>2026-09-18 06:59 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1100"/>
+  <dimension ref="A1:C1103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-18 06:59 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-19 06:57 UTC</t>
         </is>
       </c>
     </row>
@@ -16934,6 +16934,51 @@
       <c r="C1100" t="inlineStr">
         <is>
           <t>2026-09-18 06:59 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1101" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>2026-09-19 06:57 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1102" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>2026-09-19 06:57 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1103" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>2026-09-19 06:57 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1103"/>
+  <dimension ref="A1:C1106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-19 06:57 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-20 07:23 UTC</t>
         </is>
       </c>
     </row>
@@ -16979,6 +16979,51 @@
       <c r="C1103" t="inlineStr">
         <is>
           <t>2026-09-19 06:57 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1104" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>2026-09-20 07:23 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1105" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>2026-09-20 07:23 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1106" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>2026-09-20 07:23 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1106"/>
+  <dimension ref="A1:C1109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-20 07:23 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-21 07:33 UTC</t>
         </is>
       </c>
     </row>
@@ -17024,6 +17024,51 @@
       <c r="C1106" t="inlineStr">
         <is>
           <t>2026-09-20 07:23 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1107" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:33 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1108" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:33 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1109" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:33 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1109"/>
+  <dimension ref="A1:C1112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-21 07:33 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-22 07:13 UTC</t>
         </is>
       </c>
     </row>
@@ -17069,6 +17069,51 @@
       <c r="C1109" t="inlineStr">
         <is>
           <t>2026-09-21 07:33 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1110" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>2026-09-22 07:13 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1111" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>2026-09-22 07:13 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1112" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>2026-09-22 07:13 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1112"/>
+  <dimension ref="A1:C1115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-22 07:13 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-23 07:14 UTC</t>
         </is>
       </c>
     </row>
@@ -17114,6 +17114,51 @@
       <c r="C1112" t="inlineStr">
         <is>
           <t>2026-09-22 07:13 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1113" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>2026-09-23 07:14 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1114" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>2026-09-23 07:14 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1115" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>2026-09-23 07:14 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1115"/>
+  <dimension ref="A1:C1118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-23 07:14 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-24 07:05 UTC</t>
         </is>
       </c>
     </row>
@@ -17159,6 +17159,51 @@
       <c r="C1115" t="inlineStr">
         <is>
           <t>2026-09-23 07:14 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1116" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1117" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1118" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>2026-09-24 07:05 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1118"/>
+  <dimension ref="A1:C1121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-24 07:05 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-25 07:03 UTC</t>
         </is>
       </c>
     </row>
@@ -17204,6 +17204,51 @@
       <c r="C1118" t="inlineStr">
         <is>
           <t>2026-09-24 07:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1119" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>2026-09-25 07:03 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1120" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>2026-09-25 07:03 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1121" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>2026-09-25 07:03 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1121"/>
+  <dimension ref="A1:C1124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-25 07:03 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-26 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -17249,6 +17249,51 @@
       <c r="C1121" t="inlineStr">
         <is>
           <t>2026-09-25 07:03 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1122" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>2026-09-26 07:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1123" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>2026-09-26 07:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1124" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>2026-09-26 07:00 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1124"/>
+  <dimension ref="A1:C1127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-26 07:00 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-27 07:31 UTC</t>
         </is>
       </c>
     </row>
@@ -17294,6 +17294,51 @@
       <c r="C1124" t="inlineStr">
         <is>
           <t>2026-09-26 07:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1125" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>2026-09-27 07:31 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1126" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>2026-09-27 07:31 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1127" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>2026-09-27 07:31 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1127"/>
+  <dimension ref="A1:C1130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-27 07:31 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-28 08:08 UTC</t>
         </is>
       </c>
     </row>
@@ -17339,6 +17339,51 @@
       <c r="C1127" t="inlineStr">
         <is>
           <t>2026-09-27 07:31 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1128" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>2026-09-28 08:08 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1129" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>2026-09-28 08:08 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1130" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>2026-09-28 08:08 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1130"/>
+  <dimension ref="A1:C1133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-28 08:08 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-29 07:49 UTC</t>
         </is>
       </c>
     </row>
@@ -17384,6 +17384,51 @@
       <c r="C1130" t="inlineStr">
         <is>
           <t>2026-09-28 08:08 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1131" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:49 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1132" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:49 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1133" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>2026-09-29 07:49 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1133"/>
+  <dimension ref="A1:C1136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-29 07:49 UTC</t>
+          <t>Last Refreshed (UTC): 2026-09-30 07:52 UTC</t>
         </is>
       </c>
     </row>
@@ -17429,6 +17429,51 @@
       <c r="C1133" t="inlineStr">
         <is>
           <t>2026-09-29 07:49 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1134" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>2026-09-30 07:52 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1135" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>2026-09-30 07:52 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1136" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>2026-09-30 07:52 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1136"/>
+  <dimension ref="A1:C1139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-09-30 07:52 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-01 08:14 UTC</t>
         </is>
       </c>
     </row>
@@ -17474,6 +17474,51 @@
       <c r="C1136" t="inlineStr">
         <is>
           <t>2026-09-30 07:52 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1137" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>2026-10-01 08:14 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1138" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>2026-10-01 08:14 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1139" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>2026-10-01 08:14 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1139"/>
+  <dimension ref="A1:C1142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-01 08:14 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-01 12:32 UTC</t>
         </is>
       </c>
     </row>
@@ -17519,6 +17519,51 @@
       <c r="C1139" t="inlineStr">
         <is>
           <t>2026-10-01 08:14 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1140" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:32 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1141" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:32 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1142" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:32 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1142"/>
+  <dimension ref="A1:C1145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-01 12:32 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-02 07:52 UTC</t>
         </is>
       </c>
     </row>
@@ -17564,6 +17564,51 @@
       <c r="C1142" t="inlineStr">
         <is>
           <t>2026-10-01 12:32 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1143" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>2026-10-02 07:52 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1144" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>2026-10-02 07:52 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1145" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>2026-10-02 07:52 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1145"/>
+  <dimension ref="A1:C1148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-02 07:52 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-03 07:31 UTC</t>
         </is>
       </c>
     </row>
@@ -17609,6 +17609,51 @@
       <c r="C1145" t="inlineStr">
         <is>
           <t>2026-10-02 07:52 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1146" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>2026-10-03 07:31 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1147" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>2026-10-03 07:31 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1148" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>2026-10-03 07:31 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1148"/>
+  <dimension ref="A1:C1151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-03 07:31 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-04 07:42 UTC</t>
         </is>
       </c>
     </row>
@@ -17654,6 +17654,51 @@
       <c r="C1148" t="inlineStr">
         <is>
           <t>2026-10-03 07:31 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1149" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>2026-10-04 07:42 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1150" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>2026-10-04 07:42 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1151" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>2026-10-04 07:42 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1151"/>
+  <dimension ref="A1:C1154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-04 07:42 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-05 08:12 UTC</t>
         </is>
       </c>
     </row>
@@ -17699,6 +17699,51 @@
       <c r="C1151" t="inlineStr">
         <is>
           <t>2026-10-04 07:42 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1152" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>2026-10-05 08:12 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1153" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>2026-10-05 08:12 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1154" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>2026-10-05 08:12 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1154"/>
+  <dimension ref="A1:C1157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-05 08:12 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-06 08:29 UTC</t>
         </is>
       </c>
     </row>
@@ -17744,6 +17744,51 @@
       <c r="C1154" t="inlineStr">
         <is>
           <t>2026-10-05 08:12 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1155" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>2026-10-06 08:29 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1156" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>2026-10-06 08:29 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1157" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>2026-10-06 08:29 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1157"/>
+  <dimension ref="A1:C1160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-06 08:29 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-07 08:05 UTC</t>
         </is>
       </c>
     </row>
@@ -17789,6 +17789,51 @@
       <c r="C1157" t="inlineStr">
         <is>
           <t>2026-10-06 08:29 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1158" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>2026-10-07 08:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1159" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>2026-10-07 08:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1160" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>2026-10-07 08:05 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1160"/>
+  <dimension ref="A1:C1163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-07 08:05 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-08 08:21 UTC</t>
         </is>
       </c>
     </row>
@@ -17834,6 +17834,51 @@
       <c r="C1160" t="inlineStr">
         <is>
           <t>2026-10-07 08:05 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1161" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:21 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1162" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:21 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1163" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:21 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1163"/>
+  <dimension ref="A1:C1166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-08 08:21 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-09 08:24 UTC</t>
         </is>
       </c>
     </row>
@@ -17879,6 +17879,51 @@
       <c r="C1163" t="inlineStr">
         <is>
           <t>2026-10-08 08:21 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1164" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>2026-10-09 08:24 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1165" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>2026-10-09 08:24 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1166" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>2026-10-09 08:24 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1166"/>
+  <dimension ref="A1:C1169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-09 08:24 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-10 08:01 UTC</t>
         </is>
       </c>
     </row>
@@ -17924,6 +17924,51 @@
       <c r="C1166" t="inlineStr">
         <is>
           <t>2026-10-09 08:24 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1167" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>2026-10-10 08:01 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1168" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>2026-10-10 08:01 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1169" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>2026-10-10 08:01 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1169"/>
+  <dimension ref="A1:C1172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-10 08:01 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-11 08:13 UTC</t>
         </is>
       </c>
     </row>
@@ -17969,6 +17969,51 @@
       <c r="C1169" t="inlineStr">
         <is>
           <t>2026-10-10 08:01 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1170" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>2026-10-11 08:13 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1171" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>2026-10-11 08:13 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1172" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>2026-10-11 08:13 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1172"/>
+  <dimension ref="A1:C1175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-11 08:13 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-12 08:30 UTC</t>
         </is>
       </c>
     </row>
@@ -18014,6 +18014,51 @@
       <c r="C1172" t="inlineStr">
         <is>
           <t>2026-10-11 08:13 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1173" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>2026-10-12 08:30 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1174" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>2026-10-12 08:30 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1175" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>2026-10-12 08:30 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1175"/>
+  <dimension ref="A1:C1178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-12 08:30 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-13 08:52 UTC</t>
         </is>
       </c>
     </row>
@@ -18059,6 +18059,51 @@
       <c r="C1175" t="inlineStr">
         <is>
           <t>2026-10-12 08:30 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1176" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:52 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1177" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:52 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1178" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:52 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1178"/>
+  <dimension ref="A1:C1181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-13 08:52 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-14 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -18104,6 +18104,51 @@
       <c r="C1178" t="inlineStr">
         <is>
           <t>2026-10-13 08:52 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1179" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>2026-10-14 07:02 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1180" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>2026-10-14 07:02 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1181" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>2026-10-14 07:02 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1181"/>
+  <dimension ref="A1:C1184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-14 07:02 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-15 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -18149,6 +18149,51 @@
       <c r="C1181" t="inlineStr">
         <is>
           <t>2026-10-14 07:02 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1182" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1183" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1184" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:53 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1184"/>
+  <dimension ref="A1:C1187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-15 06:53 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-16 06:40 UTC</t>
         </is>
       </c>
     </row>
@@ -18194,6 +18194,51 @@
       <c r="C1184" t="inlineStr">
         <is>
           <t>2026-10-15 06:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1185" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:40 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1186" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:40 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1187" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:40 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1187"/>
+  <dimension ref="A1:C1190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-16 06:40 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-17 06:29 UTC</t>
         </is>
       </c>
     </row>
@@ -18239,6 +18239,51 @@
       <c r="C1187" t="inlineStr">
         <is>
           <t>2026-10-16 06:40 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1188" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:29 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1189" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:29 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1190" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:29 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1190"/>
+  <dimension ref="A1:C1193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-17 06:29 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-18 06:54 UTC</t>
         </is>
       </c>
     </row>
@@ -18284,6 +18284,51 @@
       <c r="C1190" t="inlineStr">
         <is>
           <t>2026-10-17 06:29 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1191" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1192" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1193" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:54 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1193"/>
+  <dimension ref="A1:C1196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-18 06:54 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-19 07:14 UTC</t>
         </is>
       </c>
     </row>
@@ -18329,6 +18329,51 @@
       <c r="C1193" t="inlineStr">
         <is>
           <t>2026-10-18 06:54 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1194" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>2026-10-19 07:14 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1195" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>2026-10-19 07:14 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1196" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>2026-10-19 07:14 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1196"/>
+  <dimension ref="A1:C1199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-19 07:14 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-20 07:04 UTC</t>
         </is>
       </c>
     </row>
@@ -18374,6 +18374,51 @@
       <c r="C1196" t="inlineStr">
         <is>
           <t>2026-10-19 07:14 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1197" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>2026-10-20 07:04 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1198" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>2026-10-20 07:04 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1199" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>2026-10-20 07:04 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1199"/>
+  <dimension ref="A1:C1202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-20 07:04 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-21 06:57 UTC</t>
         </is>
       </c>
     </row>
@@ -18419,6 +18419,51 @@
       <c r="C1199" t="inlineStr">
         <is>
           <t>2026-10-20 07:04 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1200" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:57 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1201" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:57 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1202" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:57 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1202"/>
+  <dimension ref="A1:C1205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-21 06:57 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-22 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -18464,6 +18464,51 @@
       <c r="C1202" t="inlineStr">
         <is>
           <t>2026-10-21 06:57 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1203" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>2026-10-22 07:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1204" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>2026-10-22 07:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1205" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>2026-10-22 07:00 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1205"/>
+  <dimension ref="A1:C1208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-22 07:00 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-23 06:53 UTC</t>
         </is>
       </c>
     </row>
@@ -18509,6 +18509,51 @@
       <c r="C1205" t="inlineStr">
         <is>
           <t>2026-10-22 07:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1206" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1207" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1208" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:53 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1208"/>
+  <dimension ref="A1:C1211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-23 06:53 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-24 06:49 UTC</t>
         </is>
       </c>
     </row>
@@ -18554,6 +18554,51 @@
       <c r="C1208" t="inlineStr">
         <is>
           <t>2026-10-23 06:53 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1209" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:49 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1210" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:49 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1211" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:49 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1211"/>
+  <dimension ref="A1:C1214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-24 06:49 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-25 07:13 UTC</t>
         </is>
       </c>
     </row>
@@ -18599,6 +18599,51 @@
       <c r="C1211" t="inlineStr">
         <is>
           <t>2026-10-24 06:49 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1212" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>2026-10-25 07:13 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1213" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>2026-10-25 07:13 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1214" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>2026-10-25 07:13 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1214"/>
+  <dimension ref="A1:C1217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-25 07:13 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-26 07:21 UTC</t>
         </is>
       </c>
     </row>
@@ -18644,6 +18644,51 @@
       <c r="C1214" t="inlineStr">
         <is>
           <t>2026-10-25 07:13 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1215" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>2026-10-26 07:21 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1216" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>2026-10-26 07:21 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1217" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>2026-10-26 07:21 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1217"/>
+  <dimension ref="A1:C1220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-26 07:21 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-27 07:13 UTC</t>
         </is>
       </c>
     </row>
@@ -18689,6 +18689,51 @@
       <c r="C1217" t="inlineStr">
         <is>
           <t>2026-10-26 07:21 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1218" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>2026-10-27 07:13 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1219" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>2026-10-27 07:13 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1220" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>2026-10-27 07:13 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1220"/>
+  <dimension ref="A1:C1223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-27 07:13 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-28 07:51 UTC</t>
         </is>
       </c>
     </row>
@@ -18734,6 +18734,51 @@
       <c r="C1220" t="inlineStr">
         <is>
           <t>2026-10-27 07:13 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1221" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>2026-10-28 07:51 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1222" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>2026-10-28 07:51 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1223" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>2026-10-28 07:51 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1223"/>
+  <dimension ref="A1:C1226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-28 07:51 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-29 07:57 UTC</t>
         </is>
       </c>
     </row>
@@ -18779,6 +18779,51 @@
       <c r="C1223" t="inlineStr">
         <is>
           <t>2026-10-28 07:51 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1224" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>2026-10-29 07:57 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1225" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>2026-10-29 07:57 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1226" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>2026-10-29 07:57 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1226"/>
+  <dimension ref="A1:C1229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-29 07:57 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-30 07:59 UTC</t>
         </is>
       </c>
     </row>
@@ -18824,6 +18824,51 @@
       <c r="C1226" t="inlineStr">
         <is>
           <t>2026-10-29 07:57 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1227" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>2026-10-30 07:59 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1228" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>2026-10-30 07:59 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1229" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>2026-10-30 07:59 UTC</t>
         </is>
       </c>
     </row>

--- a/04_Excel/KPI_Snapshot.xlsx
+++ b/04_Excel/KPI_Snapshot.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1229"/>
+  <dimension ref="A1:C1232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Last Refreshed (UTC): 2026-10-30 07:59 UTC</t>
+          <t>Last Refreshed (UTC): 2026-10-31 07:56 UTC</t>
         </is>
       </c>
     </row>
@@ -18869,6 +18869,51 @@
       <c r="C1229" t="inlineStr">
         <is>
           <t>2026-10-30 07:59 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B1230" t="n">
+        <v>10641558.95</v>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>2026-10-31 07:56 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>Total Customers</t>
+        </is>
+      </c>
+      <c r="B1231" t="n">
+        <v>4338</v>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>2026-10-31 07:56 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>Average Order Value</t>
+        </is>
+      </c>
+      <c r="B1232" t="n">
+        <v>2453.102570308898</v>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>2026-10-31 07:56 UTC</t>
         </is>
       </c>
     </row>
